--- a/Assets/Resource/Q/QDialogue.xlsx
+++ b/Assets/Resource/Q/QDialogue.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="30">
   <si>
     <t>segmentId</t>
   </si>
@@ -68,6 +68,57 @@
   </si>
   <si>
     <t>end</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>嘉斯林</t>
+  </si>
+  <si>
+    <t>小家伙，你好啊。</t>
+  </si>
+  <si>
+    <t>我的框可以让你的小车达到【反重力】的效果。</t>
+  </si>
+  <si>
+    <t>用我的能力越过鸿沟吧！</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>希</t>
+  </si>
+  <si>
+    <t>你好......</t>
+  </si>
+  <si>
+    <t>小车是我的发明......</t>
+  </si>
+  <si>
+    <t>我的框可以让它加速......</t>
+  </si>
+  <si>
+    <t>务必尝试。</t>
+  </si>
+  <si>
+    <t>Goal</t>
+  </si>
+  <si>
+    <t>【？？？】</t>
+  </si>
+  <si>
+    <t>（电流故障的滋滋声）</t>
+  </si>
+  <si>
+    <t>看，那个就是数据包。</t>
+  </si>
+  <si>
+    <t>对，你的目标是让小车到达数据包所在的区域。</t>
+  </si>
+  <si>
+    <t>加油。</t>
   </si>
 </sst>
 </file>
@@ -683,8 +734,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -998,111 +1052,298 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="4" max="4" width="37.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="1">
+        <v>3</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1">
+        <v>3</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>12</v>
       </c>
     </row>

--- a/Assets/Resource/Q/QDialogue.xlsx
+++ b/Assets/Resource/Q/QDialogue.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="34">
   <si>
     <t>segmentId</t>
   </si>
@@ -119,6 +119,18 @@
   </si>
   <si>
     <t>加油。</t>
+  </si>
+  <si>
+    <t>哦对了。</t>
+  </si>
+  <si>
+    <t>你可以通过“W”“A”“S”“D”控制视野。</t>
+  </si>
+  <si>
+    <t>另外还可以把已部署的框拖拽到屏幕最下边来删除这个框。</t>
+  </si>
+  <si>
+    <t>祝你好运！</t>
   </si>
 </sst>
 </file>
@@ -1052,7 +1064,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="4" max="4" width="37.6666666666667" customWidth="1"/>
@@ -1343,7 +1355,75 @@
       <c r="D17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1">
+        <v>4</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="1">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="1">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="1">
+        <v>7</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" t="s">
         <v>12</v>
       </c>
     </row>

--- a/Assets/Resource/Q/QDialogue.xlsx
+++ b/Assets/Resource/Q/QDialogue.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="30">
   <si>
     <t>segmentId</t>
   </si>
@@ -119,18 +119,6 @@
   </si>
   <si>
     <t>加油。</t>
-  </si>
-  <si>
-    <t>哦对了。</t>
-  </si>
-  <si>
-    <t>你可以通过“W”“A”“S”“D”控制视野。</t>
-  </si>
-  <si>
-    <t>另外还可以把已部署的框拖拽到屏幕最下边来删除这个框。</t>
-  </si>
-  <si>
-    <t>祝你好运！</t>
   </si>
 </sst>
 </file>
@@ -1064,7 +1052,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="4" max="4" width="37.6666666666667" customWidth="1"/>
@@ -1355,75 +1343,7 @@
       <c r="D17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="1">
-        <v>4</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="1">
-        <v>5</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="1">
-        <v>6</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="1">
-        <v>7</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="E17" s="1" t="s">
         <v>12</v>
       </c>
     </row>
